--- a/public/templates/athlete_list.xlsx
+++ b/public/templates/athlete_list.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12300"/>
+    <workbookView windowWidth="27945" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -207,7 +207,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -215,14 +215,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -230,7 +230,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -238,7 +238,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -246,7 +246,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -254,7 +254,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -262,14 +262,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -277,7 +277,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -285,7 +285,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -293,14 +293,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -308,47 +308,47 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,12 +441,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -477,12 +471,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -531,12 +519,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -574,12 +556,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,80 +793,80 @@
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -898,13 +874,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -915,12 +891,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -960,60 +930,57 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常規" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
+    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
+    <cellStyle name="註釋" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
+    <cellStyle name="標題" xfId="10" builtinId="15"/>
+    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
+    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
+    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
+    <cellStyle name="輸入" xfId="16" builtinId="20"/>
+    <cellStyle name="輸出" xfId="17" builtinId="21"/>
+    <cellStyle name="計算" xfId="18" builtinId="22"/>
+    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
+    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
+    <cellStyle name="匯總" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="適中" xfId="24" builtinId="28"/>
+    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1287,8 +1254,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1328,13 +1295,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
@@ -1361,292 +1322,302 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="K3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="K4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="11:15">
-      <c r="K3" s="7" t="s">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="K5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="11:15">
-      <c r="K4" s="7" t="s">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="K6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="11:15">
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="11:15">
-      <c r="K6" s="8" t="s">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="K8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="11:15">
-      <c r="K7" s="6" t="s">
+      <c r="L8" s="9"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="K9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="11:15">
-      <c r="K8" s="7" t="s">
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="K10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="11:15">
-      <c r="K9" s="7" t="s">
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="K11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="11:15">
-      <c r="K10" s="10" t="s">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="K12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="11:15">
-      <c r="K11" s="10" t="s">
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="K13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="11:15">
-      <c r="K12" s="11" t="s">
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="K14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="11:15">
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="11:15">
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="K16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="11:15">
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="11:15">
-      <c r="K16" s="13" t="s">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="11:15">
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="11:15">
+      <c r="K18" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" spans="11:15">
-      <c r="K17" s="6" t="s">
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="11:15">
+      <c r="K19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L19" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" spans="11:15">
-      <c r="K18" s="7" t="s">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="11:15">
+      <c r="K20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="11:15">
-      <c r="K19" s="7" t="s">
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="11:15">
+      <c r="K21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="M21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="11:15">
-      <c r="K20" s="12" t="s">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="11:15">
+      <c r="K22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="11:15">
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="11:15">
-      <c r="K22" s="16" t="s">
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="11:15">
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="11:15">
+      <c r="K24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="11:15">
-      <c r="K23" s="19" t="s">
+      <c r="L24" s="15"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="11:15">
+      <c r="K25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L23" s="20"/>
-      <c r="M23" s="6" t="s">
+      <c r="L25" s="18"/>
+      <c r="M25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="11:15">
-      <c r="K24" s="21" t="s">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="11:15">
+      <c r="K26" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L24" s="22"/>
-      <c r="M24" s="7" t="s">
+      <c r="L26" s="20"/>
+      <c r="M26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="11:15">
-      <c r="K25" s="12"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="11:15">
-      <c r="K26" s="23" t="s">
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="11:15">
+      <c r="K27" s="10"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="11:15">
+      <c r="K28" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="L26" s="24"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" spans="11:15">
-      <c r="K27" s="6" t="s">
+      <c r="L28" s="22"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="11:15">
+      <c r="K29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L29" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-    </row>
-    <row r="28" spans="11:15">
-      <c r="K28" s="7" t="s">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="11:15">
+      <c r="K30" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="L28" s="25">
+      <c r="L30" s="7">
         <v>1</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="11:15">
-      <c r="K29" s="12" t="s">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="11:15">
+      <c r="K31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K28:L28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
